--- a/www/ig/fhir/ror/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/www/ig/fhir/ror/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="153">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:54:01+00:00</t>
+    <t>2026-04-29T15:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -384,9 +384,6 @@
 </t>
   </si>
   <si>
-    <t>publicPrisEnCharge</t>
-  </si>
-  <si>
     <t>Extension.extension:ageRange</t>
   </si>
   <si>
@@ -463,9 +460,6 @@
 qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
-    <t>ageMin</t>
-  </si>
-  <si>
     <t>./low</t>
   </si>
   <si>
@@ -485,9 +479,6 @@
   </si>
   <si>
     <t>Range.high</t>
-  </si>
-  <si>
-    <t>ageMax</t>
   </si>
   <si>
     <t>./high</t>
@@ -1804,7 +1795,7 @@
         <v>119</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>110</v>
@@ -1812,13 +1803,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -1920,7 +1911,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>100</v>
@@ -2026,7 +2017,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>102</v>
@@ -2132,7 +2123,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>104</v>
@@ -2175,7 +2166,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>76</v>
@@ -2240,7 +2231,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>112</v>
@@ -2266,7 +2257,7 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>114</v>
@@ -2346,10 +2337,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2452,14 +2443,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2481,13 +2472,13 @@
         <v>91</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2560,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2583,19 +2574,19 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="K17" t="s" s="2">
+      <c r="L17" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2645,7 +2636,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2657,21 +2648,21 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2691,19 +2682,19 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="K18" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="K18" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="L18" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2753,7 +2744,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2765,13 +2756,13 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19">
@@ -2910,7 +2901,7 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>114</v>
